--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:02:23+00:00</t>
+    <t>2023-09-21T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T09:50:54+00:00</t>
+    <t>2023-09-21T10:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T10:44:28+00:00</t>
+    <t>2023-09-21T12:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T12:08:39+00:00</t>
+    <t>2023-09-21T12:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T12:39:02+00:00</t>
+    <t>2023-09-21T14:50:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -733,11 +733,11 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrPatient)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
-    <t>Patient concerné par ce document. La ressource référencée peut être présente sous l’élément DocumentReference.contained ou via le champ identifier.</t>
+    <t>Who/what is the subject of the document</t>
   </si>
   <si>
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
@@ -802,7 +802,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|Device|http://interopsante.org/fhir/StructureDefinition/FrPatient|http://interopsante.org/fhir/StructureDefinition/FrRelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -836,7 +836,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
 </t>
   </si>
   <si>
@@ -1524,6 +1524,10 @@
   </si>
   <si>
     <t>DocumentReference.context.sourcePatientInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrPatient)
+</t>
   </si>
   <si>
     <t>Référence vers la ressource Patient titulaire du dossier.</t>
@@ -1880,7 +1884,7 @@
     <col min="8" max="8" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="77.93359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -9446,13 +9450,13 @@
         <v>35</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>226</v>
+        <v>476</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>229</v>
@@ -9538,15 +9542,15 @@
         <v>35</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9569,16 +9573,16 @@
         <v>35</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9628,7 +9632,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -9646,13 +9650,13 @@
         <v>35</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>35</v>
@@ -9661,7 +9665,7 @@
         <v>35</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T14:50:45+00:00</t>
+    <t>2023-09-22T07:44:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T07:44:14+00:00</t>
+    <t>2023-09-22T09:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T09:20:33+00:00</t>
+    <t>2023-09-22T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T09:23:37+00:00</t>
+    <t>2023-09-22T12:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T12:19:21+00:00</t>
+    <t>2023-09-25T11:57:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-25T11:57:57+00:00</t>
+    <t>2023-10-02T07:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T07:48:38+00:00</t>
+    <t>2023-10-02T08:19:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T08:19:52+00:00</t>
+    <t>2023-10-02T10:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T10:10:17+00:00</t>
+    <t>2023-10-02T11:49:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T11:49:05+00:00</t>
+    <t>2023-10-02T12:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T12:02:40+00:00</t>
+    <t>2023-10-03T08:22:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-03T08:22:32+00:00</t>
+    <t>2023-10-04T13:47:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-04T13:47:01+00:00</t>
+    <t>2023-10-05T12:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-05T12:28:13+00:00</t>
+    <t>2023-10-05T13:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-05T13:01:35+00:00</t>
+    <t>2023-10-06T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-06T10:30:12+00:00</t>
+    <t>2023-10-06T12:10:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-06T12:10:03+00:00</t>
+    <t>2023-10-06T14:30:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-06T14:30:45+00:00</t>
+    <t>2023-10-09T06:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-09T06:42:29+00:00</t>
+    <t>2023-10-09T14:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
